--- a/BADesign/Excel/PatrolPath.xlsx
+++ b/BADesign/Excel/PatrolPath.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="시트1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="PatrolPath" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>

--- a/BADesign/Excel/PatrolPath.xlsx
+++ b/BADesign/Excel/PatrolPath.xlsx
@@ -31,7 +31,7 @@
     <t>First_Test_Monster_Path</t>
   </si>
   <si>
-    <t>(1270, 1170, 480), (1389.2, 1401.9, 439.2), (1689.8, 1173.2, 358.7), (1940.0, 670.0, 300.0)</t>
+    <t>(2850.0, -600.0, 0.0), (3170.0, -790.0, 0.0), (2923.1, -1109.8, 0.0), (2709.3, -1571.8, 0.0), (2495.7, -1093.8, 0.0), (2273.5, -1687.1, 0.0)</t>
   </si>
 </sst>
 </file>
@@ -330,7 +330,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="3" max="3" width="17.63"/>
-    <col customWidth="1" min="4" max="4" width="61.13"/>
+    <col customWidth="1" min="4" max="4" width="90.0"/>
   </cols>
   <sheetData>
     <row r="1">
